--- a/artfynd/A 28834-2026 artfynd.xlsx
+++ b/artfynd/A 28834-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135998284</v>
       </c>
       <c r="B3" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28834-2026 artfynd.xlsx
+++ b/artfynd/A 28834-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135998284</v>
       </c>
       <c r="B3" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28834-2026 artfynd.xlsx
+++ b/artfynd/A 28834-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135998284</v>
       </c>
       <c r="B3" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28834-2026 artfynd.xlsx
+++ b/artfynd/A 28834-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135998284</v>
       </c>
       <c r="B3" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
